--- a/public/assets/example/contoh-import-inject-mutasi-sewing.xlsx
+++ b/public/assets/example/contoh-import-inject-mutasi-sewing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASBAZAR\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\nds_wip_local_main\public\assets\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602EA3C6-EF05-4BF1-969C-3416DA2E793D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09323E26-BE90-4A2A-92DF-5FBB925603B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
   <si>
     <t>tgl_saldo</t>
   </si>
@@ -163,13 +163,19 @@
   </si>
   <si>
     <t>SEWING</t>
+  </si>
+  <si>
+    <t>pc_terima</t>
+  </si>
+  <si>
+    <t>pc_packing_scan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -223,9 +229,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -263,7 +269,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -369,7 +375,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -511,7 +517,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -519,8 +525,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AN7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -560,7 +566,7 @@
     <col min="38" max="38" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -675,8 +681,14 @@
       <c r="AL1" t="s">
         <v>37</v>
       </c>
+      <c r="AM1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40">
       <c r="A2" s="1">
         <v>46170</v>
       </c>
@@ -699,7 +711,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40">
       <c r="A3" s="1">
         <v>46170</v>
       </c>
@@ -722,13 +734,13 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40">
       <c r="A7" s="1"/>
     </row>
   </sheetData>

--- a/public/assets/example/contoh-import-inject-mutasi-sewing.xlsx
+++ b/public/assets/example/contoh-import-inject-mutasi-sewing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\nds_wip_local_main\public\assets\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09323E26-BE90-4A2A-92DF-5FBB925603B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2ED4FE3-B246-4401-9844-A429A6DF7DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$3:$G$246</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$G$247</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,154 +28,178 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
-  <si>
-    <t>tgl_saldo</t>
-  </si>
-  <si>
-    <t>type_saldo</t>
-  </si>
-  <si>
-    <t>buyer</t>
-  </si>
-  <si>
-    <t>ws</t>
-  </si>
-  <si>
-    <t>styleno</t>
-  </si>
-  <si>
-    <t>color</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>qty_loading</t>
-  </si>
-  <si>
-    <t>input_rework_sewing</t>
-  </si>
-  <si>
-    <t>input_rework_spotcleaning</t>
-  </si>
-  <si>
-    <t>input_rework_mending</t>
-  </si>
-  <si>
-    <t>defect_sewing</t>
-  </si>
-  <si>
-    <t>defect_spotcleaning</t>
-  </si>
-  <si>
-    <t>defect_mending</t>
-  </si>
-  <si>
-    <t>qty_sew_reject</t>
-  </si>
-  <si>
-    <t>qty_sewing</t>
-  </si>
-  <si>
-    <t>input_rework_sewing_f</t>
-  </si>
-  <si>
-    <t>input_rework_spotcleaning_f</t>
-  </si>
-  <si>
-    <t>input_rework_mending_f</t>
-  </si>
-  <si>
-    <t>defect_sewing_f</t>
-  </si>
-  <si>
-    <t>defect_spotcleaning_f</t>
-  </si>
-  <si>
-    <t>defect_mending_f</t>
-  </si>
-  <si>
-    <t>qty_fin_reject</t>
-  </si>
-  <si>
-    <t>qty_finishing</t>
-  </si>
-  <si>
-    <t>total_in_sp</t>
-  </si>
-  <si>
-    <t>rework_sp</t>
-  </si>
-  <si>
-    <t>defect_sp</t>
-  </si>
-  <si>
-    <t>reject_sp</t>
-  </si>
-  <si>
-    <t>rft_sp</t>
-  </si>
-  <si>
-    <t>total_defect_sewing</t>
-  </si>
-  <si>
-    <t>total_input_rework_sewing</t>
-  </si>
-  <si>
-    <t>total_defect_spotcleaning</t>
-  </si>
-  <si>
-    <t>total_input_rework_spotcleaning</t>
-  </si>
-  <si>
-    <t>total_defect_mending</t>
-  </si>
-  <si>
-    <t>total_input_rework_mending</t>
-  </si>
-  <si>
-    <t>qty_reject_in</t>
-  </si>
-  <si>
-    <t>qty_rejected</t>
-  </si>
-  <si>
-    <t>qty_reworked</t>
-  </si>
-  <si>
-    <t>AMAZON</t>
-  </si>
-  <si>
-    <t>AMZ/0226/002</t>
-  </si>
-  <si>
-    <t>AEGL92682S25 REP</t>
-  </si>
-  <si>
-    <t>BLACK/PANTONE 19-3911 TCX BLAC</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>2T</t>
-  </si>
-  <si>
     <t>SEWING</t>
   </si>
   <si>
-    <t>pc_terima</t>
-  </si>
-  <si>
-    <t>pc_packing_scan</t>
+    <t>Loading Qty</t>
+  </si>
+  <si>
+    <t>Rework Sewing</t>
+  </si>
+  <si>
+    <t>Rework Sewing Spotcleaning</t>
+  </si>
+  <si>
+    <t>Rework Sewing Mending</t>
+  </si>
+  <si>
+    <t>Defect Sewing</t>
+  </si>
+  <si>
+    <t>Defect Spotcleaning</t>
+  </si>
+  <si>
+    <t>Defect Mending</t>
+  </si>
+  <si>
+    <t>Reject Sewing Qty</t>
+  </si>
+  <si>
+    <t>Defect Sewing Spotcleaning</t>
+  </si>
+  <si>
+    <t>Defect Sewing Mending</t>
+  </si>
+  <si>
+    <t>Sewing Qty</t>
+  </si>
+  <si>
+    <t>Rework QC Finishing</t>
+  </si>
+  <si>
+    <t>Rework QC Finishing Spotcleaning</t>
+  </si>
+  <si>
+    <t>Rework QC Finishing Mending</t>
+  </si>
+  <si>
+    <t>Defect QC Finishing Sewing</t>
+  </si>
+  <si>
+    <t>Defect QC Finishing Spotcleaning</t>
+  </si>
+  <si>
+    <t>Defect QC Finishing Mending</t>
+  </si>
+  <si>
+    <t>Reject QC Finishing</t>
+  </si>
+  <si>
+    <t>QC Finishing Qty</t>
+  </si>
+  <si>
+    <t>Finshing Process IN</t>
+  </si>
+  <si>
+    <t>Defect Finishing Process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rework Finishing Process </t>
+  </si>
+  <si>
+    <t>Reject Finishing Process</t>
+  </si>
+  <si>
+    <t>RFT Finishing Process</t>
+  </si>
+  <si>
+    <t>Rework Spotcleaning</t>
+  </si>
+  <si>
+    <t>Rework Mending</t>
+  </si>
+  <si>
+    <t>Keluar Gudang Stok</t>
+  </si>
+  <si>
+    <t>QC Reject In</t>
+  </si>
+  <si>
+    <t>Keluar Sewing</t>
+  </si>
+  <si>
+    <t>Packing RFT</t>
+  </si>
+  <si>
+    <t>Packing Reject</t>
+  </si>
+  <si>
+    <t>Packing Keluar</t>
+  </si>
+  <si>
+    <t>Packing Central Packing Scan</t>
+  </si>
+  <si>
+    <t>Packing Central Terima</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Style</t>
+  </si>
+  <si>
+    <t>WS</t>
+  </si>
+  <si>
+    <t>Buyer</t>
+  </si>
+  <si>
+    <t>Tipe Saldo</t>
+  </si>
+  <si>
+    <t>Tanggal</t>
+  </si>
+  <si>
+    <t>FINISHING</t>
+  </si>
+  <si>
+    <t>PACKING</t>
+  </si>
+  <si>
+    <t>REJECTED</t>
+  </si>
+  <si>
+    <t>FINISHING PROCESS</t>
+  </si>
+  <si>
+    <t>BEYOND YOGA</t>
+  </si>
+  <si>
+    <t>BYN/0226/005</t>
+  </si>
+  <si>
+    <t>SD7972D SPACEDYE GO-TO MENS HOODIE</t>
+  </si>
+  <si>
+    <t>DARKEST NIGHT</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>DEFECT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -525,223 +549,432 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AQ8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="26" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="21" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.85546875" customWidth="1"/>
+    <col min="14" max="14" width="25.7109375" customWidth="1"/>
+    <col min="15" max="15" width="19.5703125" customWidth="1"/>
+    <col min="16" max="16" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.7109375" customWidth="1"/>
+    <col min="18" max="18" width="34.28515625" customWidth="1"/>
+    <col min="19" max="19" width="32" customWidth="1"/>
+    <col min="20" max="20" width="26.85546875" customWidth="1"/>
+    <col min="21" max="21" width="32" customWidth="1"/>
+    <col min="22" max="22" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.5703125" customWidth="1"/>
+    <col min="24" max="24" width="19.140625" customWidth="1"/>
+    <col min="25" max="25" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="26" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="27.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" t="s">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+      <c r="AF5">
+        <v>1</v>
+      </c>
+      <c r="AG5">
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B6" t="s">
         <v>45</v>
       </c>
-      <c r="AN1" t="s">
-        <v>46</v>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:40">
-      <c r="A2" s="1">
-        <v>46170</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B7" t="s">
         <v>44</v>
       </c>
-      <c r="C2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" t="s">
-        <v>42</v>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AN7">
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <v>1</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:40">
-      <c r="A3" s="1">
-        <v>46170</v>
-      </c>
-      <c r="B3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:40">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" spans="1:40">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:40">
-      <c r="A7" s="1"/>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
